--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555269</v>
+        <v>124555442</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,50 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491017</v>
+        <v>490962</v>
       </c>
       <c r="R3" t="n">
-        <v>6869226</v>
+        <v>6869305</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,19 +881,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555330</v>
+        <v>124555800</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -933,17 +929,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490997</v>
+        <v>491078</v>
       </c>
       <c r="R4" t="n">
-        <v>6869240</v>
+        <v>6869479</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555207</v>
+        <v>124555330</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,47 +1007,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491027</v>
+        <v>490997</v>
       </c>
       <c r="R5" t="n">
-        <v>6869192</v>
+        <v>6869240</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1110,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555289</v>
+        <v>124555216</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1145,7 +1132,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1155,17 +1142,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491008</v>
+        <v>491016</v>
       </c>
       <c r="R6" t="n">
-        <v>6869214</v>
+        <v>6869188</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555517</v>
+        <v>124555235</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,41 +1220,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491020</v>
+        <v>491014</v>
       </c>
       <c r="R7" t="n">
-        <v>6869351</v>
+        <v>6869213</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555800</v>
+        <v>124555269</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,41 +1331,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491078</v>
+        <v>491017</v>
       </c>
       <c r="R8" t="n">
-        <v>6869479</v>
+        <v>6869226</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1430,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555253</v>
+        <v>124555289</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1470,14 +1475,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491020</v>
+        <v>491008</v>
       </c>
       <c r="R9" t="n">
-        <v>6869220</v>
+        <v>6869214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1647,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555221</v>
+        <v>124555260</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,47 +1664,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491024</v>
+        <v>490993</v>
       </c>
       <c r="R11" t="n">
-        <v>6869198</v>
+        <v>6869192</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,7 +1754,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555235</v>
+        <v>124555207</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1793,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1803,17 +1799,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491014</v>
+        <v>491027</v>
       </c>
       <c r="R12" t="n">
-        <v>6869213</v>
+        <v>6869192</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,22 +1853,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555260</v>
+        <v>124555341</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,37 +1881,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490993</v>
+        <v>490971</v>
       </c>
       <c r="R13" t="n">
-        <v>6869192</v>
+        <v>6869235</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,22 +1955,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555341</v>
+        <v>124555517</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490971</v>
+        <v>491020</v>
       </c>
       <c r="R14" t="n">
-        <v>6869235</v>
+        <v>6869351</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2073,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555773</v>
+        <v>124555280</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2109,17 +2105,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491115</v>
+        <v>491004</v>
       </c>
       <c r="R15" t="n">
-        <v>6869473</v>
+        <v>6869214</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2163,22 +2159,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555943</v>
+        <v>124555773</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,50 +2183,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491108</v>
+        <v>491115</v>
       </c>
       <c r="R16" t="n">
-        <v>6869470</v>
+        <v>6869473</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,22 +2261,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555442</v>
+        <v>124555253</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,38 +2285,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490962</v>
+        <v>491020</v>
       </c>
       <c r="R17" t="n">
-        <v>6869305</v>
+        <v>6869220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,11 +2360,6 @@
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2381,22 +2372,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555280</v>
+        <v>124555221</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,41 +2396,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491004</v>
+        <v>491024</v>
       </c>
       <c r="R18" t="n">
-        <v>6869214</v>
+        <v>6869198</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555216</v>
+        <v>124555943</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491016</v>
+        <v>491108</v>
       </c>
       <c r="R19" t="n">
-        <v>6869188</v>
+        <v>6869470</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124556002</v>
+        <v>124555773</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491116</v>
+        <v>491115</v>
       </c>
       <c r="R2" t="n">
-        <v>6869470</v>
+        <v>6869473</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555442</v>
+        <v>124555289</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490962</v>
+        <v>491008</v>
       </c>
       <c r="R3" t="n">
-        <v>6869305</v>
+        <v>6869214</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555800</v>
+        <v>124555269</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +900,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491078</v>
+        <v>491017</v>
       </c>
       <c r="R4" t="n">
-        <v>6869479</v>
+        <v>6869226</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555330</v>
+        <v>124555280</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1031,17 +1035,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490997</v>
+        <v>491004</v>
       </c>
       <c r="R5" t="n">
-        <v>6869240</v>
+        <v>6869214</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555216</v>
+        <v>124555442</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,50 +1113,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491016</v>
+        <v>490962</v>
       </c>
       <c r="R6" t="n">
-        <v>6869188</v>
+        <v>6869305</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,6 +1177,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,22 +1196,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555235</v>
+        <v>124555260</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,50 +1220,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491014</v>
+        <v>490993</v>
       </c>
       <c r="R7" t="n">
-        <v>6869213</v>
+        <v>6869192</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,22 +1298,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555269</v>
+        <v>124555517</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,47 +1322,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491017</v>
+        <v>491020</v>
       </c>
       <c r="R8" t="n">
-        <v>6869226</v>
+        <v>6869351</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1430,7 +1412,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555289</v>
+        <v>124555216</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1465,7 +1447,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1475,17 +1457,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491008</v>
+        <v>491016</v>
       </c>
       <c r="R9" t="n">
-        <v>6869214</v>
+        <v>6869188</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1511,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555994</v>
+        <v>124555341</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,50 +1535,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491147</v>
+        <v>490971</v>
       </c>
       <c r="R10" t="n">
-        <v>6869404</v>
+        <v>6869235</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1640,22 +1613,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555260</v>
+        <v>124555943</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,41 +1637,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490993</v>
+        <v>491108</v>
       </c>
       <c r="R11" t="n">
-        <v>6869192</v>
+        <v>6869470</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,19 +1724,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555207</v>
+        <v>124555994</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1789,7 +1771,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1803,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491027</v>
+        <v>491147</v>
       </c>
       <c r="R12" t="n">
-        <v>6869192</v>
+        <v>6869404</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1865,10 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555341</v>
+        <v>124555330</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,37 +1863,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490971</v>
+        <v>490997</v>
       </c>
       <c r="R13" t="n">
-        <v>6869235</v>
+        <v>6869240</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,22 +1937,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555517</v>
+        <v>124556002</v>
       </c>
       <c r="B14" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,38 +1961,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491020</v>
+        <v>491116</v>
       </c>
       <c r="R14" t="n">
-        <v>6869351</v>
+        <v>6869470</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2069,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555280</v>
+        <v>124555207</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,41 +2072,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491004</v>
+        <v>491027</v>
       </c>
       <c r="R15" t="n">
-        <v>6869214</v>
+        <v>6869192</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,19 +2159,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555773</v>
+        <v>124555800</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2207,17 +2207,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491115</v>
+        <v>491078</v>
       </c>
       <c r="R16" t="n">
-        <v>6869473</v>
+        <v>6869479</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2261,19 +2261,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555253</v>
+        <v>124555221</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2318,17 +2318,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491020</v>
+        <v>491024</v>
       </c>
       <c r="R17" t="n">
-        <v>6869220</v>
+        <v>6869198</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2372,19 +2372,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555221</v>
+        <v>124555235</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2429,17 +2429,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491024</v>
+        <v>491014</v>
       </c>
       <c r="R18" t="n">
-        <v>6869198</v>
+        <v>6869213</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555943</v>
+        <v>124555253</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491108</v>
+        <v>491020</v>
       </c>
       <c r="R19" t="n">
-        <v>6869470</v>
+        <v>6869220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555773</v>
+        <v>124555442</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491115</v>
+        <v>490962</v>
       </c>
       <c r="R2" t="n">
-        <v>6869473</v>
+        <v>6869305</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555289</v>
+        <v>124555207</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491008</v>
+        <v>491027</v>
       </c>
       <c r="R3" t="n">
-        <v>6869214</v>
+        <v>6869192</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555269</v>
+        <v>124555994</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -923,7 +928,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -933,17 +938,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491017</v>
+        <v>491147</v>
       </c>
       <c r="R4" t="n">
-        <v>6869226</v>
+        <v>6869404</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,19 +992,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555280</v>
+        <v>124555260</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1035,17 +1040,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491004</v>
+        <v>490993</v>
       </c>
       <c r="R5" t="n">
-        <v>6869214</v>
+        <v>6869192</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1094,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555442</v>
+        <v>124555216</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,41 +1118,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490962</v>
+        <v>491016</v>
       </c>
       <c r="R6" t="n">
-        <v>6869305</v>
+        <v>6869188</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,19 +1205,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555260</v>
+        <v>124555800</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1244,17 +1253,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490993</v>
+        <v>491078</v>
       </c>
       <c r="R7" t="n">
-        <v>6869192</v>
+        <v>6869479</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,22 +1307,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555517</v>
+        <v>124555289</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,41 +1331,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491020</v>
+        <v>491008</v>
       </c>
       <c r="R8" t="n">
-        <v>6869351</v>
+        <v>6869214</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1400,22 +1418,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555216</v>
+        <v>124555330</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,50 +1442,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491016</v>
+        <v>490997</v>
       </c>
       <c r="R9" t="n">
-        <v>6869188</v>
+        <v>6869240</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,22 +1520,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555341</v>
+        <v>124555221</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,41 +1544,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490971</v>
+        <v>491024</v>
       </c>
       <c r="R10" t="n">
-        <v>6869235</v>
+        <v>6869198</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,22 +1631,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555943</v>
+        <v>124555517</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,50 +1655,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491108</v>
+        <v>491020</v>
       </c>
       <c r="R11" t="n">
-        <v>6869470</v>
+        <v>6869351</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555994</v>
+        <v>124555341</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1748,50 +1757,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491147</v>
+        <v>490971</v>
       </c>
       <c r="R12" t="n">
-        <v>6869404</v>
+        <v>6869235</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,22 +1835,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555330</v>
+        <v>124556002</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,41 +1859,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490997</v>
+        <v>491116</v>
       </c>
       <c r="R13" t="n">
-        <v>6869240</v>
+        <v>6869470</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,19 +1946,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556002</v>
+        <v>124555943</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1984,7 +1993,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1998,13 +2007,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491116</v>
+        <v>491108</v>
       </c>
       <c r="R14" t="n">
         <v>6869470</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2060,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555207</v>
+        <v>124555773</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,47 +2081,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491027</v>
+        <v>491115</v>
       </c>
       <c r="R15" t="n">
-        <v>6869192</v>
+        <v>6869473</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555800</v>
+        <v>124555253</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,38 +2183,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491078</v>
+        <v>491020</v>
       </c>
       <c r="R16" t="n">
-        <v>6869479</v>
+        <v>6869220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2282,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555221</v>
+        <v>124555235</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2308,7 +2317,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2318,17 +2327,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491024</v>
+        <v>491014</v>
       </c>
       <c r="R17" t="n">
-        <v>6869198</v>
+        <v>6869213</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2372,19 +2381,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555235</v>
+        <v>124555269</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2419,7 +2428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2433,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491014</v>
+        <v>491017</v>
       </c>
       <c r="R18" t="n">
-        <v>6869213</v>
+        <v>6869226</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555253</v>
+        <v>124555280</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,50 +2516,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491020</v>
+        <v>491004</v>
       </c>
       <c r="R19" t="n">
-        <v>6869220</v>
+        <v>6869214</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555442</v>
+        <v>124555341</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490962</v>
+        <v>490971</v>
       </c>
       <c r="R2" t="n">
-        <v>6869305</v>
+        <v>6869235</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555207</v>
+        <v>124555221</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491027</v>
+        <v>491024</v>
       </c>
       <c r="R3" t="n">
-        <v>6869192</v>
+        <v>6869198</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555994</v>
+        <v>124555517</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,50 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491147</v>
+        <v>491020</v>
       </c>
       <c r="R4" t="n">
-        <v>6869404</v>
+        <v>6869351</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555260</v>
+        <v>124555280</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1040,17 +1026,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490993</v>
+        <v>491004</v>
       </c>
       <c r="R5" t="n">
-        <v>6869192</v>
+        <v>6869214</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,19 +1080,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555216</v>
+        <v>124555253</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1155,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491016</v>
+        <v>491020</v>
       </c>
       <c r="R6" t="n">
-        <v>6869188</v>
+        <v>6869220</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555800</v>
+        <v>124555207</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,41 +1215,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491078</v>
+        <v>491027</v>
       </c>
       <c r="R7" t="n">
-        <v>6869479</v>
+        <v>6869192</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,19 +1302,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555289</v>
+        <v>124555994</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1354,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1368,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491008</v>
+        <v>491147</v>
       </c>
       <c r="R8" t="n">
-        <v>6869214</v>
+        <v>6869404</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555330</v>
+        <v>124556002</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,41 +1437,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490997</v>
+        <v>491116</v>
       </c>
       <c r="R9" t="n">
-        <v>6869240</v>
+        <v>6869470</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1520,19 +1524,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555221</v>
+        <v>124555216</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1577,17 +1581,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491024</v>
+        <v>491016</v>
       </c>
       <c r="R10" t="n">
-        <v>6869198</v>
+        <v>6869188</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,22 +1635,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555517</v>
+        <v>124555800</v>
       </c>
       <c r="B11" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491020</v>
+        <v>491078</v>
       </c>
       <c r="R11" t="n">
-        <v>6869351</v>
+        <v>6869479</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555341</v>
+        <v>124555269</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,38 +1761,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490971</v>
+        <v>491017</v>
       </c>
       <c r="R12" t="n">
-        <v>6869235</v>
+        <v>6869226</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1847,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556002</v>
+        <v>124555442</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,50 +1872,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491116</v>
+        <v>490962</v>
       </c>
       <c r="R13" t="n">
-        <v>6869470</v>
+        <v>6869305</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,6 +1936,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,19 +1955,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555943</v>
+        <v>124555289</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1993,7 +2002,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2003,14 +2012,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491108</v>
+        <v>491008</v>
       </c>
       <c r="R14" t="n">
-        <v>6869470</v>
+        <v>6869214</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2057,12 +2066,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2171,7 +2180,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555253</v>
+        <v>124555943</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2206,7 +2215,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2220,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491020</v>
+        <v>491108</v>
       </c>
       <c r="R16" t="n">
-        <v>6869220</v>
+        <v>6869470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555235</v>
+        <v>124555330</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,50 +2303,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491014</v>
+        <v>490997</v>
       </c>
       <c r="R17" t="n">
-        <v>6869213</v>
+        <v>6869240</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,22 +2381,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555269</v>
+        <v>124555260</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,50 +2405,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491017</v>
+        <v>490993</v>
       </c>
       <c r="R18" t="n">
-        <v>6869226</v>
+        <v>6869192</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,22 +2483,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555280</v>
+        <v>124555235</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,41 +2507,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491004</v>
+        <v>491014</v>
       </c>
       <c r="R19" t="n">
-        <v>6869214</v>
+        <v>6869213</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555341</v>
+        <v>124555221</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490971</v>
+        <v>491024</v>
       </c>
       <c r="R2" t="n">
-        <v>6869235</v>
+        <v>6869198</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555221</v>
+        <v>124555341</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491024</v>
+        <v>490971</v>
       </c>
       <c r="R3" t="n">
-        <v>6869198</v>
+        <v>6869235</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +876,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555800</v>
+        <v>124555269</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,41 +1659,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491078</v>
+        <v>491017</v>
       </c>
       <c r="R11" t="n">
-        <v>6869479</v>
+        <v>6869226</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555269</v>
+        <v>124555800</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1761,50 +1770,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491017</v>
+        <v>491078</v>
       </c>
       <c r="R12" t="n">
-        <v>6869226</v>
+        <v>6869479</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555221</v>
+        <v>124555330</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491024</v>
+        <v>490997</v>
       </c>
       <c r="R2" t="n">
-        <v>6869198</v>
+        <v>6869240</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555341</v>
+        <v>124555442</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490971</v>
+        <v>490962</v>
       </c>
       <c r="R3" t="n">
-        <v>6869235</v>
+        <v>6869305</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555517</v>
+        <v>124555773</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491020</v>
+        <v>491115</v>
       </c>
       <c r="R4" t="n">
-        <v>6869351</v>
+        <v>6869473</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555280</v>
+        <v>124555221</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +998,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491004</v>
+        <v>491024</v>
       </c>
       <c r="R5" t="n">
-        <v>6869214</v>
+        <v>6869198</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,19 +1085,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555253</v>
+        <v>124555994</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1127,7 +1132,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1137,17 +1142,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491020</v>
+        <v>491147</v>
       </c>
       <c r="R6" t="n">
-        <v>6869220</v>
+        <v>6869404</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1196,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555207</v>
+        <v>124555289</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491027</v>
+        <v>491008</v>
       </c>
       <c r="R7" t="n">
-        <v>6869192</v>
+        <v>6869214</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555994</v>
+        <v>124555517</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,50 +1331,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491147</v>
+        <v>491020</v>
       </c>
       <c r="R8" t="n">
-        <v>6869404</v>
+        <v>6869351</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,19 +1409,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124556002</v>
+        <v>124555235</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1474,13 +1470,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491116</v>
+        <v>491014</v>
       </c>
       <c r="R9" t="n">
-        <v>6869470</v>
+        <v>6869213</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1647,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555269</v>
+        <v>124555341</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,47 +1655,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491017</v>
+        <v>490971</v>
       </c>
       <c r="R11" t="n">
-        <v>6869226</v>
+        <v>6869235</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1758,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555800</v>
+        <v>124555269</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,41 +1757,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491078</v>
+        <v>491017</v>
       </c>
       <c r="R12" t="n">
-        <v>6869479</v>
+        <v>6869226</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555442</v>
+        <v>124555280</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1896,17 +1892,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490962</v>
+        <v>491004</v>
       </c>
       <c r="R13" t="n">
-        <v>6869305</v>
+        <v>6869214</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1936,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,19 +1946,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555289</v>
+        <v>124556002</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2002,7 +1993,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2012,17 +2003,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491008</v>
+        <v>491116</v>
       </c>
       <c r="R14" t="n">
-        <v>6869214</v>
+        <v>6869470</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,22 +2057,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555773</v>
+        <v>124555943</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,41 +2081,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491115</v>
+        <v>491108</v>
       </c>
       <c r="R15" t="n">
-        <v>6869473</v>
+        <v>6869470</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2168,22 +2168,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555943</v>
+        <v>124555260</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,50 +2192,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491108</v>
+        <v>490993</v>
       </c>
       <c r="R16" t="n">
-        <v>6869470</v>
+        <v>6869192</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2279,22 +2270,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555330</v>
+        <v>124555207</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,38 +2294,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490997</v>
+        <v>491027</v>
       </c>
       <c r="R17" t="n">
-        <v>6869240</v>
+        <v>6869192</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2393,7 +2393,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555260</v>
+        <v>124555800</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2429,17 +2429,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490993</v>
+        <v>491078</v>
       </c>
       <c r="R18" t="n">
-        <v>6869192</v>
+        <v>6869479</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555235</v>
+        <v>124555253</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491014</v>
+        <v>491020</v>
       </c>
       <c r="R19" t="n">
-        <v>6869213</v>
+        <v>6869220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555330</v>
+        <v>124555943</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490997</v>
+        <v>491108</v>
       </c>
       <c r="R2" t="n">
-        <v>6869240</v>
+        <v>6869470</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555442</v>
+        <v>124555994</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +798,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490962</v>
+        <v>491147</v>
       </c>
       <c r="R3" t="n">
-        <v>6869305</v>
+        <v>6869404</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555221</v>
+        <v>124555216</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1031,17 +1044,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491024</v>
+        <v>491016</v>
       </c>
       <c r="R5" t="n">
-        <v>6869198</v>
+        <v>6869188</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,19 +1098,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555994</v>
+        <v>124556002</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1132,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1142,17 +1155,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491147</v>
+        <v>491116</v>
       </c>
       <c r="R6" t="n">
-        <v>6869404</v>
+        <v>6869470</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1209,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555289</v>
+        <v>124555280</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,50 +1233,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491008</v>
+        <v>491004</v>
       </c>
       <c r="R7" t="n">
         <v>6869214</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,22 +1311,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555517</v>
+        <v>124555800</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,21 +1339,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1359,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491020</v>
+        <v>491078</v>
       </c>
       <c r="R8" t="n">
-        <v>6869351</v>
+        <v>6869479</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555235</v>
+        <v>124555253</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1456,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1470,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491014</v>
+        <v>491020</v>
       </c>
       <c r="R9" t="n">
-        <v>6869213</v>
+        <v>6869220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555216</v>
+        <v>124555341</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,47 +1548,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491016</v>
+        <v>490971</v>
       </c>
       <c r="R10" t="n">
-        <v>6869188</v>
+        <v>6869235</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1643,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555341</v>
+        <v>124555260</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,37 +1654,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490971</v>
+        <v>490993</v>
       </c>
       <c r="R11" t="n">
-        <v>6869235</v>
+        <v>6869192</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,12 +1728,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555280</v>
+        <v>124555517</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491004</v>
+        <v>491020</v>
       </c>
       <c r="R13" t="n">
-        <v>6869214</v>
+        <v>6869351</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1958,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556002</v>
+        <v>124555221</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2003,17 +1998,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491116</v>
+        <v>491024</v>
       </c>
       <c r="R14" t="n">
-        <v>6869470</v>
+        <v>6869198</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,22 +2052,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555943</v>
+        <v>124555330</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,50 +2076,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491108</v>
+        <v>490997</v>
       </c>
       <c r="R15" t="n">
-        <v>6869470</v>
+        <v>6869240</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2168,22 +2154,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555260</v>
+        <v>124555289</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,41 +2178,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490993</v>
+        <v>491008</v>
       </c>
       <c r="R16" t="n">
-        <v>6869192</v>
+        <v>6869214</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2282,7 +2277,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555207</v>
+        <v>124555235</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2317,7 +2312,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2327,17 +2322,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491027</v>
+        <v>491014</v>
       </c>
       <c r="R17" t="n">
-        <v>6869192</v>
+        <v>6869213</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,22 +2376,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555800</v>
+        <v>124555207</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,41 +2400,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491078</v>
+        <v>491027</v>
       </c>
       <c r="R18" t="n">
-        <v>6869479</v>
+        <v>6869192</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,22 +2487,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555253</v>
+        <v>124555442</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,47 +2511,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491020</v>
+        <v>490962</v>
       </c>
       <c r="R19" t="n">
-        <v>6869220</v>
+        <v>6869305</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2582,6 +2577,11 @@
           <t>2025-04-29</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2594,12 +2594,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555943</v>
+        <v>124555216</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491108</v>
+        <v>491016</v>
       </c>
       <c r="R2" t="n">
-        <v>6869470</v>
+        <v>6869188</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555994</v>
+        <v>124555260</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491147</v>
+        <v>490993</v>
       </c>
       <c r="R3" t="n">
-        <v>6869404</v>
+        <v>6869192</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555773</v>
+        <v>124555442</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -937,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491115</v>
+        <v>490962</v>
       </c>
       <c r="R4" t="n">
-        <v>6869473</v>
+        <v>6869305</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,6 +964,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555216</v>
+        <v>124555280</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,47 +1007,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491016</v>
+        <v>491004</v>
       </c>
       <c r="R5" t="n">
-        <v>6869188</v>
+        <v>6869214</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1110,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124556002</v>
+        <v>124555994</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1145,7 +1132,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1155,17 +1142,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491116</v>
+        <v>491147</v>
       </c>
       <c r="R6" t="n">
-        <v>6869470</v>
+        <v>6869404</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,19 +1196,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555280</v>
+        <v>124555800</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1261,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491004</v>
+        <v>491078</v>
       </c>
       <c r="R7" t="n">
-        <v>6869214</v>
+        <v>6869479</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555800</v>
+        <v>124555235</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,38 +1322,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491078</v>
+        <v>491014</v>
       </c>
       <c r="R8" t="n">
-        <v>6869479</v>
+        <v>6869213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555253</v>
+        <v>124555269</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1460,7 +1456,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1474,13 +1470,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491020</v>
+        <v>491017</v>
       </c>
       <c r="R9" t="n">
-        <v>6869220</v>
+        <v>6869226</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555341</v>
+        <v>124555253</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,41 +1544,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490971</v>
+        <v>491020</v>
       </c>
       <c r="R10" t="n">
-        <v>6869235</v>
+        <v>6869220</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555260</v>
+        <v>124556002</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,41 +1655,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490993</v>
+        <v>491116</v>
       </c>
       <c r="R11" t="n">
-        <v>6869192</v>
+        <v>6869470</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,19 +1742,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555269</v>
+        <v>124555207</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1775,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1785,17 +1799,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491017</v>
+        <v>491027</v>
       </c>
       <c r="R12" t="n">
-        <v>6869226</v>
+        <v>6869192</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,12 +1853,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1953,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555221</v>
+        <v>124555943</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1988,7 +2002,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1998,17 +2012,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491024</v>
+        <v>491108</v>
       </c>
       <c r="R14" t="n">
-        <v>6869198</v>
+        <v>6869470</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,19 +2066,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555330</v>
+        <v>124555773</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2104,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490997</v>
+        <v>491115</v>
       </c>
       <c r="R15" t="n">
-        <v>6869240</v>
+        <v>6869473</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2166,7 +2180,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555289</v>
+        <v>124555221</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2201,7 +2215,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2215,13 +2229,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491008</v>
+        <v>491024</v>
       </c>
       <c r="R16" t="n">
-        <v>6869214</v>
+        <v>6869198</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555235</v>
+        <v>124555341</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,50 +2303,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491014</v>
+        <v>490971</v>
       </c>
       <c r="R17" t="n">
-        <v>6869213</v>
+        <v>6869235</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2388,7 +2393,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555207</v>
+        <v>124555289</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2423,7 +2428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2437,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491027</v>
+        <v>491008</v>
       </c>
       <c r="R18" t="n">
-        <v>6869192</v>
+        <v>6869214</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555442</v>
+        <v>124555330</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2539,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490962</v>
+        <v>490997</v>
       </c>
       <c r="R19" t="n">
-        <v>6869305</v>
+        <v>6869240</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2575,11 +2580,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555442</v>
+        <v>124555280</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,17 +924,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490962</v>
+        <v>491004</v>
       </c>
       <c r="R4" t="n">
-        <v>6869305</v>
+        <v>6869214</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555280</v>
+        <v>124555442</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1031,17 +1026,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491004</v>
+        <v>490962</v>
       </c>
       <c r="R5" t="n">
-        <v>6869214</v>
+        <v>6869305</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,12 +1085,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555773</v>
+        <v>124555221</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,38 +2090,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491115</v>
+        <v>491024</v>
       </c>
       <c r="R15" t="n">
-        <v>6869473</v>
+        <v>6869198</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2180,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555221</v>
+        <v>124555773</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,47 +2201,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491024</v>
+        <v>491115</v>
       </c>
       <c r="R16" t="n">
-        <v>6869198</v>
+        <v>6869473</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555341</v>
+        <v>124555289</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,41 +2303,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490971</v>
+        <v>491008</v>
       </c>
       <c r="R17" t="n">
-        <v>6869235</v>
+        <v>6869214</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,22 +2390,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555289</v>
+        <v>124555341</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,50 +2414,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491008</v>
+        <v>490971</v>
       </c>
       <c r="R18" t="n">
-        <v>6869214</v>
+        <v>6869235</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555216</v>
+        <v>124556002</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491016</v>
+        <v>491116</v>
       </c>
       <c r="R2" t="n">
-        <v>6869188</v>
+        <v>6869470</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555260</v>
+        <v>124555207</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490993</v>
+        <v>491027</v>
       </c>
       <c r="R3" t="n">
         <v>6869192</v>
@@ -888,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555280</v>
+        <v>124555221</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +909,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491004</v>
+        <v>491024</v>
       </c>
       <c r="R4" t="n">
-        <v>6869214</v>
+        <v>6869198</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,19 +996,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555442</v>
+        <v>124555280</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,17 +1044,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490962</v>
+        <v>491004</v>
       </c>
       <c r="R5" t="n">
-        <v>6869305</v>
+        <v>6869214</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,22 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555994</v>
+        <v>124555330</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,47 +1122,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491147</v>
+        <v>490997</v>
       </c>
       <c r="R6" t="n">
-        <v>6869404</v>
+        <v>6869240</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1208,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555800</v>
+        <v>124555253</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,38 +1224,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491078</v>
+        <v>491020</v>
       </c>
       <c r="R7" t="n">
-        <v>6869479</v>
+        <v>6869220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555235</v>
+        <v>124555517</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,50 +1335,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491014</v>
+        <v>491020</v>
       </c>
       <c r="R8" t="n">
-        <v>6869213</v>
+        <v>6869351</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555269</v>
+        <v>124555235</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1456,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1470,13 +1474,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491017</v>
+        <v>491014</v>
       </c>
       <c r="R9" t="n">
-        <v>6869226</v>
+        <v>6869213</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555253</v>
+        <v>124555943</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1567,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1581,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491020</v>
+        <v>491108</v>
       </c>
       <c r="R10" t="n">
-        <v>6869220</v>
+        <v>6869470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124556002</v>
+        <v>124555442</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,50 +1659,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491116</v>
+        <v>490962</v>
       </c>
       <c r="R11" t="n">
-        <v>6869470</v>
+        <v>6869305</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,6 +1723,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,22 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555207</v>
+        <v>124555341</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,50 +1766,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491027</v>
+        <v>490971</v>
       </c>
       <c r="R12" t="n">
-        <v>6869192</v>
+        <v>6869235</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,22 +1844,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555517</v>
+        <v>124555800</v>
       </c>
       <c r="B13" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1905,13 +1896,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491020</v>
+        <v>491078</v>
       </c>
       <c r="R13" t="n">
-        <v>6869351</v>
+        <v>6869479</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555943</v>
+        <v>124555773</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,50 +1970,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491108</v>
+        <v>491115</v>
       </c>
       <c r="R14" t="n">
-        <v>6869470</v>
+        <v>6869473</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,22 +2048,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555221</v>
+        <v>124555260</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,47 +2072,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491024</v>
+        <v>490993</v>
       </c>
       <c r="R15" t="n">
-        <v>6869198</v>
+        <v>6869192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2189,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555773</v>
+        <v>124555216</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,41 +2174,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491115</v>
+        <v>491016</v>
       </c>
       <c r="R16" t="n">
-        <v>6869473</v>
+        <v>6869188</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2279,12 +2261,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2402,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555341</v>
+        <v>124555269</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,38 +2396,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490971</v>
+        <v>491017</v>
       </c>
       <c r="R18" t="n">
-        <v>6869235</v>
+        <v>6869226</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2504,10 +2495,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555330</v>
+        <v>124555994</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,38 +2507,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490997</v>
+        <v>491147</v>
       </c>
       <c r="R19" t="n">
-        <v>6869240</v>
+        <v>6869404</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124556002</v>
+        <v>124555260</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491116</v>
+        <v>490993</v>
       </c>
       <c r="R2" t="n">
-        <v>6869470</v>
+        <v>6869192</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -774,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555207</v>
+        <v>124556002</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -831,17 +822,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491027</v>
+        <v>491116</v>
       </c>
       <c r="R3" t="n">
-        <v>6869192</v>
+        <v>6869470</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555221</v>
+        <v>124555800</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,50 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491024</v>
+        <v>491078</v>
       </c>
       <c r="R4" t="n">
-        <v>6869198</v>
+        <v>6869479</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555280</v>
+        <v>124555207</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,41 +1002,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491004</v>
+        <v>491027</v>
       </c>
       <c r="R5" t="n">
-        <v>6869214</v>
+        <v>6869192</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555330</v>
+        <v>124555253</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,41 +1113,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490997</v>
+        <v>491020</v>
       </c>
       <c r="R6" t="n">
-        <v>6869240</v>
+        <v>6869220</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,19 +1200,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555253</v>
+        <v>124555216</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491020</v>
+        <v>491016</v>
       </c>
       <c r="R7" t="n">
-        <v>6869220</v>
+        <v>6869188</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555517</v>
+        <v>124555773</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,37 +1339,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491020</v>
+        <v>491115</v>
       </c>
       <c r="R8" t="n">
-        <v>6869351</v>
+        <v>6869473</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,22 +1413,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555235</v>
+        <v>124555517</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,50 +1437,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491014</v>
+        <v>491020</v>
       </c>
       <c r="R9" t="n">
-        <v>6869213</v>
+        <v>6869351</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555943</v>
+        <v>124555289</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1571,7 +1562,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1581,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491108</v>
+        <v>491008</v>
       </c>
       <c r="R10" t="n">
-        <v>6869470</v>
+        <v>6869214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,22 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555442</v>
+        <v>124555269</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,41 +1650,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490962</v>
+        <v>491017</v>
       </c>
       <c r="R11" t="n">
-        <v>6869305</v>
+        <v>6869226</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1723,11 +1723,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,22 +1737,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555341</v>
+        <v>124555994</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,41 +1761,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490971</v>
+        <v>491147</v>
       </c>
       <c r="R12" t="n">
-        <v>6869235</v>
+        <v>6869404</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555800</v>
+        <v>124555341</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,13 +1900,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491078</v>
+        <v>490971</v>
       </c>
       <c r="R13" t="n">
-        <v>6869479</v>
+        <v>6869235</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555773</v>
+        <v>124555330</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1998,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491115</v>
+        <v>490997</v>
       </c>
       <c r="R14" t="n">
-        <v>6869473</v>
+        <v>6869240</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2060,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555260</v>
+        <v>124555943</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,41 +2076,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490993</v>
+        <v>491108</v>
       </c>
       <c r="R15" t="n">
-        <v>6869192</v>
+        <v>6869470</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,22 +2163,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555216</v>
+        <v>124555280</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,47 +2187,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491016</v>
+        <v>491004</v>
       </c>
       <c r="R16" t="n">
-        <v>6869188</v>
+        <v>6869214</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2273,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555289</v>
+        <v>124555442</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,47 +2289,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491008</v>
+        <v>490962</v>
       </c>
       <c r="R17" t="n">
-        <v>6869214</v>
+        <v>6869305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,6 +2353,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2384,7 +2384,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555269</v>
+        <v>124555235</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491017</v>
+        <v>491014</v>
       </c>
       <c r="R18" t="n">
-        <v>6869226</v>
+        <v>6869213</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555994</v>
+        <v>124555221</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491147</v>
+        <v>491024</v>
       </c>
       <c r="R19" t="n">
-        <v>6869404</v>
+        <v>6869198</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555260</v>
+        <v>124555269</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490993</v>
+        <v>491017</v>
       </c>
       <c r="R2" t="n">
-        <v>6869192</v>
+        <v>6869226</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +774,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124556002</v>
+        <v>124555994</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -822,17 +831,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491116</v>
+        <v>491147</v>
       </c>
       <c r="R3" t="n">
-        <v>6869470</v>
+        <v>6869404</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555800</v>
+        <v>124555221</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +909,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491078</v>
+        <v>491024</v>
       </c>
       <c r="R4" t="n">
-        <v>6869479</v>
+        <v>6869198</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,22 +996,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555207</v>
+        <v>124555773</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,47 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491027</v>
+        <v>491115</v>
       </c>
       <c r="R5" t="n">
-        <v>6869192</v>
+        <v>6869473</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1101,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555253</v>
+        <v>124555235</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1136,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1150,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491020</v>
+        <v>491014</v>
       </c>
       <c r="R6" t="n">
-        <v>6869220</v>
+        <v>6869213</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555216</v>
+        <v>124555442</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,50 +1233,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491016</v>
+        <v>490962</v>
       </c>
       <c r="R7" t="n">
-        <v>6869188</v>
+        <v>6869305</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,6 +1297,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,22 +1316,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555773</v>
+        <v>124555943</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,41 +1340,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491115</v>
+        <v>491108</v>
       </c>
       <c r="R8" t="n">
-        <v>6869473</v>
+        <v>6869470</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,22 +1427,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555517</v>
+        <v>124555330</v>
       </c>
       <c r="B9" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,37 +1455,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491020</v>
+        <v>490997</v>
       </c>
       <c r="R9" t="n">
-        <v>6869351</v>
+        <v>6869240</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,22 +1529,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555289</v>
+        <v>124555800</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,47 +1553,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491008</v>
+        <v>491078</v>
       </c>
       <c r="R10" t="n">
-        <v>6869214</v>
+        <v>6869479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,19 +1631,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555269</v>
+        <v>124555289</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1673,7 +1678,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1683,17 +1688,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491017</v>
+        <v>491008</v>
       </c>
       <c r="R11" t="n">
-        <v>6869226</v>
+        <v>6869214</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,19 +1742,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555994</v>
+        <v>124555207</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1784,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491147</v>
+        <v>491027</v>
       </c>
       <c r="R12" t="n">
-        <v>6869404</v>
+        <v>6869192</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555341</v>
+        <v>124555517</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,21 +1881,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490971</v>
+        <v>491020</v>
       </c>
       <c r="R13" t="n">
-        <v>6869235</v>
+        <v>6869351</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1962,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555330</v>
+        <v>124555253</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,41 +1979,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490997</v>
+        <v>491020</v>
       </c>
       <c r="R14" t="n">
-        <v>6869240</v>
+        <v>6869220</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,19 +2066,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555943</v>
+        <v>124555216</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2099,7 +2113,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2113,13 +2127,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491108</v>
+        <v>491016</v>
       </c>
       <c r="R15" t="n">
-        <v>6869470</v>
+        <v>6869188</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555280</v>
+        <v>124555341</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2191,21 +2205,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491004</v>
+        <v>490971</v>
       </c>
       <c r="R16" t="n">
-        <v>6869214</v>
+        <v>6869235</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2277,10 +2291,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555442</v>
+        <v>124556002</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,41 +2303,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490962</v>
+        <v>491116</v>
       </c>
       <c r="R17" t="n">
-        <v>6869305</v>
+        <v>6869470</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,11 +2376,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,22 +2390,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555235</v>
+        <v>124555280</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,50 +2414,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491014</v>
+        <v>491004</v>
       </c>
       <c r="R18" t="n">
-        <v>6869213</v>
+        <v>6869214</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2495,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555221</v>
+        <v>124555260</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,47 +2516,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491024</v>
+        <v>490993</v>
       </c>
       <c r="R19" t="n">
-        <v>6869198</v>
+        <v>6869192</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -1754,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555207</v>
+        <v>124555517</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,50 +1766,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491027</v>
+        <v>491020</v>
       </c>
       <c r="R12" t="n">
-        <v>6869192</v>
+        <v>6869351</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1853,22 +1844,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555517</v>
+        <v>124555207</v>
       </c>
       <c r="B13" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,41 +1868,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491020</v>
+        <v>491027</v>
       </c>
       <c r="R13" t="n">
-        <v>6869351</v>
+        <v>6869192</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,12 +1955,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555442</v>
+        <v>124555943</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,38 +1233,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490962</v>
+        <v>491108</v>
       </c>
       <c r="R7" t="n">
-        <v>6869305</v>
+        <v>6869470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,11 +1308,6 @@
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1316,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555943</v>
+        <v>124555442</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,47 +1344,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491108</v>
+        <v>490962</v>
       </c>
       <c r="R8" t="n">
-        <v>6869470</v>
+        <v>6869305</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1410,11 @@
           <t>2025-04-29</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555341</v>
+        <v>124556002</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,38 +2201,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490971</v>
+        <v>491116</v>
       </c>
       <c r="R16" t="n">
-        <v>6869235</v>
+        <v>6869470</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2291,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124556002</v>
+        <v>124555341</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,47 +2312,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491116</v>
+        <v>490971</v>
       </c>
       <c r="R17" t="n">
-        <v>6869470</v>
+        <v>6869235</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555269</v>
+        <v>124555253</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491017</v>
+        <v>491020</v>
       </c>
       <c r="R2" t="n">
-        <v>6869226</v>
+        <v>6869220</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555994</v>
+        <v>124555330</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491147</v>
+        <v>490997</v>
       </c>
       <c r="R3" t="n">
-        <v>6869404</v>
+        <v>6869240</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555221</v>
+        <v>124555800</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,50 +900,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491024</v>
+        <v>491078</v>
       </c>
       <c r="R4" t="n">
-        <v>6869198</v>
+        <v>6869479</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,19 +978,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555773</v>
+        <v>124555442</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1048,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491115</v>
+        <v>490962</v>
       </c>
       <c r="R5" t="n">
-        <v>6869473</v>
+        <v>6869305</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555235</v>
+        <v>124555773</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,50 +1109,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491014</v>
+        <v>491115</v>
       </c>
       <c r="R6" t="n">
-        <v>6869213</v>
+        <v>6869473</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,19 +1187,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555943</v>
+        <v>124555994</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1256,7 +1234,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1266,17 +1244,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491108</v>
+        <v>491147</v>
       </c>
       <c r="R7" t="n">
-        <v>6869470</v>
+        <v>6869404</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,22 +1298,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555442</v>
+        <v>124555235</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,38 +1322,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490962</v>
+        <v>491014</v>
       </c>
       <c r="R8" t="n">
-        <v>6869305</v>
+        <v>6869213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1397,6 @@
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1427,19 +1409,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555330</v>
+        <v>124555280</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1475,17 +1457,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490997</v>
+        <v>491004</v>
       </c>
       <c r="R9" t="n">
-        <v>6869240</v>
+        <v>6869214</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1511,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555800</v>
+        <v>124555341</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,13 +1563,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491078</v>
+        <v>490971</v>
       </c>
       <c r="R10" t="n">
-        <v>6869479</v>
+        <v>6869235</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555289</v>
+        <v>124555260</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,50 +1637,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491008</v>
+        <v>490993</v>
       </c>
       <c r="R11" t="n">
-        <v>6869214</v>
+        <v>6869192</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555517</v>
+        <v>124556002</v>
       </c>
       <c r="B12" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,38 +1739,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491020</v>
+        <v>491116</v>
       </c>
       <c r="R12" t="n">
-        <v>6869351</v>
+        <v>6869470</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1856,7 +1838,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555207</v>
+        <v>124555269</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1891,7 +1873,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1901,17 +1883,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491027</v>
+        <v>491017</v>
       </c>
       <c r="R13" t="n">
-        <v>6869192</v>
+        <v>6869226</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,22 +1937,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555253</v>
+        <v>124555517</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,37 +1961,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
@@ -2019,10 +1992,10 @@
         <v>491020</v>
       </c>
       <c r="R14" t="n">
-        <v>6869220</v>
+        <v>6869351</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2078,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555216</v>
+        <v>124555207</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2113,7 +2086,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2123,17 +2096,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491016</v>
+        <v>491027</v>
       </c>
       <c r="R15" t="n">
-        <v>6869188</v>
+        <v>6869192</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,19 +2150,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124556002</v>
+        <v>124555216</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2238,10 +2211,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491116</v>
+        <v>491016</v>
       </c>
       <c r="R16" t="n">
-        <v>6869470</v>
+        <v>6869188</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2300,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555341</v>
+        <v>124555943</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,41 +2285,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490971</v>
+        <v>491108</v>
       </c>
       <c r="R17" t="n">
-        <v>6869235</v>
+        <v>6869470</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2402,10 +2384,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555280</v>
+        <v>124555221</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2414,41 +2396,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491004</v>
+        <v>491024</v>
       </c>
       <c r="R18" t="n">
-        <v>6869214</v>
+        <v>6869198</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,22 +2483,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555260</v>
+        <v>124555289</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,41 +2507,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490993</v>
+        <v>491008</v>
       </c>
       <c r="R19" t="n">
-        <v>6869192</v>
+        <v>6869214</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555253</v>
+        <v>124555800</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491020</v>
+        <v>491078</v>
       </c>
       <c r="R2" t="n">
-        <v>6869220</v>
+        <v>6869479</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555330</v>
+        <v>124555260</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490997</v>
+        <v>490993</v>
       </c>
       <c r="R3" t="n">
-        <v>6869240</v>
+        <v>6869192</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555800</v>
+        <v>124555235</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +891,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491078</v>
+        <v>491014</v>
       </c>
       <c r="R4" t="n">
-        <v>6869479</v>
+        <v>6869213</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555442</v>
+        <v>124556002</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,41 +1002,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490962</v>
+        <v>491116</v>
       </c>
       <c r="R5" t="n">
-        <v>6869305</v>
+        <v>6869470</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,11 +1075,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,22 +1089,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555773</v>
+        <v>124555341</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,37 +1117,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491115</v>
+        <v>490971</v>
       </c>
       <c r="R6" t="n">
-        <v>6869473</v>
+        <v>6869235</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1187,19 +1191,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555994</v>
+        <v>124555253</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1244,17 +1248,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491147</v>
+        <v>491020</v>
       </c>
       <c r="R7" t="n">
-        <v>6869404</v>
+        <v>6869220</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1302,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555235</v>
+        <v>124555289</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1355,14 +1359,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491014</v>
+        <v>491008</v>
       </c>
       <c r="R8" t="n">
-        <v>6869213</v>
+        <v>6869214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,19 +1413,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555280</v>
+        <v>124555330</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1457,17 +1461,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491004</v>
+        <v>490997</v>
       </c>
       <c r="R9" t="n">
-        <v>6869214</v>
+        <v>6869240</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,22 +1515,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555341</v>
+        <v>124555773</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,37 +1543,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490971</v>
+        <v>491115</v>
       </c>
       <c r="R10" t="n">
-        <v>6869235</v>
+        <v>6869473</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1613,22 +1617,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555260</v>
+        <v>124555207</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,35 +1641,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490993</v>
+        <v>491027</v>
       </c>
       <c r="R11" t="n">
         <v>6869192</v>
@@ -1727,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124556002</v>
+        <v>124555280</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,47 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491116</v>
+        <v>491004</v>
       </c>
       <c r="R12" t="n">
-        <v>6869470</v>
+        <v>6869214</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1949,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555517</v>
+        <v>124555943</v>
       </c>
       <c r="B14" t="n">
-        <v>78455</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1961,41 +1965,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491020</v>
+        <v>491108</v>
       </c>
       <c r="R14" t="n">
-        <v>6869351</v>
+        <v>6869470</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2051,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555207</v>
+        <v>124555517</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,50 +2076,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491027</v>
+        <v>491020</v>
       </c>
       <c r="R15" t="n">
-        <v>6869192</v>
+        <v>6869351</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2150,19 +2154,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555216</v>
+        <v>124555221</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2207,17 +2211,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491016</v>
+        <v>491024</v>
       </c>
       <c r="R16" t="n">
-        <v>6869188</v>
+        <v>6869198</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2261,22 +2265,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555943</v>
+        <v>124555442</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,47 +2289,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491108</v>
+        <v>490962</v>
       </c>
       <c r="R17" t="n">
-        <v>6869470</v>
+        <v>6869305</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,6 +2355,11 @@
           <t>2025-04-29</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2372,19 +2372,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555221</v>
+        <v>124555216</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2429,17 +2429,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491024</v>
+        <v>491016</v>
       </c>
       <c r="R18" t="n">
-        <v>6869198</v>
+        <v>6869188</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555289</v>
+        <v>124555994</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491008</v>
+        <v>491147</v>
       </c>
       <c r="R19" t="n">
-        <v>6869214</v>
+        <v>6869404</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555800</v>
+        <v>124555253</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491078</v>
+        <v>491020</v>
       </c>
       <c r="R2" t="n">
-        <v>6869479</v>
+        <v>6869220</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555260</v>
+        <v>124555442</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490993</v>
+        <v>490962</v>
       </c>
       <c r="R3" t="n">
-        <v>6869192</v>
+        <v>6869305</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +862,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555235</v>
+        <v>124555800</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +905,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491014</v>
+        <v>491078</v>
       </c>
       <c r="R4" t="n">
-        <v>6869213</v>
+        <v>6869479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124556002</v>
+        <v>124555943</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1030,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,13 +1044,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491116</v>
+        <v>491108</v>
       </c>
       <c r="R5" t="n">
         <v>6869470</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555341</v>
+        <v>124555216</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,38 +1118,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490971</v>
+        <v>491016</v>
       </c>
       <c r="R6" t="n">
-        <v>6869235</v>
+        <v>6869188</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1203,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555253</v>
+        <v>124555260</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,50 +1229,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491020</v>
+        <v>490993</v>
       </c>
       <c r="R7" t="n">
-        <v>6869220</v>
+        <v>6869192</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,19 +1307,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555289</v>
+        <v>124556002</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1349,7 +1354,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1359,17 +1364,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491008</v>
+        <v>491116</v>
       </c>
       <c r="R8" t="n">
-        <v>6869214</v>
+        <v>6869470</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,19 +1418,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555330</v>
+        <v>124555773</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1465,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490997</v>
+        <v>491115</v>
       </c>
       <c r="R9" t="n">
-        <v>6869240</v>
+        <v>6869473</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1527,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555773</v>
+        <v>124555994</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,38 +1544,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491115</v>
+        <v>491147</v>
       </c>
       <c r="R10" t="n">
-        <v>6869473</v>
+        <v>6869404</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1629,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555207</v>
+        <v>124555280</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,50 +1655,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491027</v>
+        <v>491004</v>
       </c>
       <c r="R11" t="n">
-        <v>6869192</v>
+        <v>6869214</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,22 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555280</v>
+        <v>124555341</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491004</v>
+        <v>490971</v>
       </c>
       <c r="R12" t="n">
-        <v>6869214</v>
+        <v>6869235</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1953,7 +1958,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555943</v>
+        <v>124555207</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1988,7 +1993,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1998,17 +2003,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491108</v>
+        <v>491027</v>
       </c>
       <c r="R14" t="n">
-        <v>6869470</v>
+        <v>6869192</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2052,22 +2057,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555517</v>
+        <v>124555330</v>
       </c>
       <c r="B15" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,37 +2085,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491020</v>
+        <v>490997</v>
       </c>
       <c r="R15" t="n">
-        <v>6869351</v>
+        <v>6869240</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2154,19 +2159,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555221</v>
+        <v>124555235</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2201,7 +2206,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2211,17 +2216,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491024</v>
+        <v>491014</v>
       </c>
       <c r="R16" t="n">
-        <v>6869198</v>
+        <v>6869213</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2265,22 +2270,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555442</v>
+        <v>124555517</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,37 +2298,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490962</v>
+        <v>491020</v>
       </c>
       <c r="R17" t="n">
-        <v>6869305</v>
+        <v>6869351</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,11 +2358,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,19 +2372,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555216</v>
+        <v>124555221</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2429,17 +2429,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491016</v>
+        <v>491024</v>
       </c>
       <c r="R18" t="n">
-        <v>6869188</v>
+        <v>6869198</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555994</v>
+        <v>124555289</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491147</v>
+        <v>491008</v>
       </c>
       <c r="R19" t="n">
-        <v>6869404</v>
+        <v>6869214</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555253</v>
+        <v>124555341</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491020</v>
+        <v>490971</v>
       </c>
       <c r="R2" t="n">
-        <v>6869220</v>
+        <v>6869235</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555442</v>
+        <v>124555800</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490962</v>
+        <v>491078</v>
       </c>
       <c r="R3" t="n">
-        <v>6869305</v>
+        <v>6869479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +855,6 @@
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555800</v>
+        <v>124555773</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -929,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491078</v>
+        <v>491115</v>
       </c>
       <c r="R4" t="n">
-        <v>6869479</v>
+        <v>6869473</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,19 +969,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555943</v>
+        <v>124555253</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,7 +1016,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1044,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491108</v>
+        <v>491020</v>
       </c>
       <c r="R5" t="n">
-        <v>6869470</v>
+        <v>6869220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555216</v>
+        <v>124555221</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1151,17 +1137,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491016</v>
+        <v>491024</v>
       </c>
       <c r="R6" t="n">
-        <v>6869188</v>
+        <v>6869198</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,22 +1191,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555260</v>
+        <v>124555269</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,41 +1215,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490993</v>
+        <v>491017</v>
       </c>
       <c r="R7" t="n">
-        <v>6869192</v>
+        <v>6869226</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,19 +1302,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124556002</v>
+        <v>124555207</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1354,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1364,17 +1359,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491116</v>
+        <v>491027</v>
       </c>
       <c r="R8" t="n">
-        <v>6869470</v>
+        <v>6869192</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,22 +1413,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555773</v>
+        <v>124555289</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,41 +1437,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491115</v>
+        <v>491008</v>
       </c>
       <c r="R9" t="n">
-        <v>6869473</v>
+        <v>6869214</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555994</v>
+        <v>124555280</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,50 +1548,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491147</v>
+        <v>491004</v>
       </c>
       <c r="R10" t="n">
-        <v>6869404</v>
+        <v>6869214</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,19 +1626,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555280</v>
+        <v>124555330</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1679,17 +1674,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491004</v>
+        <v>490997</v>
       </c>
       <c r="R11" t="n">
-        <v>6869214</v>
+        <v>6869240</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,22 +1728,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555341</v>
+        <v>124555216</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,38 +1752,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490971</v>
+        <v>491016</v>
       </c>
       <c r="R12" t="n">
-        <v>6869235</v>
+        <v>6869188</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1847,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555269</v>
+        <v>124555943</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1882,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1896,13 +1900,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491017</v>
+        <v>491108</v>
       </c>
       <c r="R13" t="n">
-        <v>6869226</v>
+        <v>6869470</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1958,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555207</v>
+        <v>124556002</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1993,7 +1997,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2003,17 +2007,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491027</v>
+        <v>491116</v>
       </c>
       <c r="R14" t="n">
-        <v>6869192</v>
+        <v>6869470</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,19 +2061,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555330</v>
+        <v>124555260</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2109,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490997</v>
+        <v>490993</v>
       </c>
       <c r="R15" t="n">
-        <v>6869240</v>
+        <v>6869192</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2282,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555517</v>
+        <v>124555442</v>
       </c>
       <c r="B17" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2298,37 +2302,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491020</v>
+        <v>490962</v>
       </c>
       <c r="R17" t="n">
-        <v>6869351</v>
+        <v>6869305</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2358,6 +2362,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,22 +2381,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555221</v>
+        <v>124555517</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,50 +2405,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491024</v>
+        <v>491020</v>
       </c>
       <c r="R18" t="n">
-        <v>6869198</v>
+        <v>6869351</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555289</v>
+        <v>124555994</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2544,13 +2544,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491008</v>
+        <v>491147</v>
       </c>
       <c r="R19" t="n">
-        <v>6869214</v>
+        <v>6869404</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555341</v>
+        <v>124555442</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490971</v>
+        <v>490962</v>
       </c>
       <c r="R2" t="n">
-        <v>6869235</v>
+        <v>6869305</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124555800</v>
+        <v>124555943</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +794,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491078</v>
+        <v>491108</v>
       </c>
       <c r="R3" t="n">
-        <v>6869479</v>
+        <v>6869470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555773</v>
+        <v>124555216</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +905,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491115</v>
+        <v>491016</v>
       </c>
       <c r="R4" t="n">
-        <v>6869473</v>
+        <v>6869188</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555253</v>
+        <v>124555260</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +1016,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491020</v>
+        <v>490993</v>
       </c>
       <c r="R5" t="n">
-        <v>6869220</v>
+        <v>6869192</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,22 +1094,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555221</v>
+        <v>124555517</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,50 +1118,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491024</v>
+        <v>491020</v>
       </c>
       <c r="R6" t="n">
-        <v>6869198</v>
+        <v>6869351</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,19 +1196,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555269</v>
+        <v>124555235</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491017</v>
+        <v>491014</v>
       </c>
       <c r="R7" t="n">
-        <v>6869226</v>
+        <v>6869213</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1319,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555207</v>
+        <v>124555253</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1349,7 +1354,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1359,17 +1364,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491027</v>
+        <v>491020</v>
       </c>
       <c r="R8" t="n">
-        <v>6869192</v>
+        <v>6869220</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,12 +1418,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1536,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555280</v>
+        <v>124555221</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,41 +1553,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491004</v>
+        <v>491024</v>
       </c>
       <c r="R10" t="n">
-        <v>6869214</v>
+        <v>6869198</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,12 +1640,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1740,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555216</v>
+        <v>124555773</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,50 +1766,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491016</v>
+        <v>491115</v>
       </c>
       <c r="R12" t="n">
-        <v>6869188</v>
+        <v>6869473</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,19 +1844,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124555943</v>
+        <v>124556002</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1886,7 +1891,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,13 +1905,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491108</v>
+        <v>491116</v>
       </c>
       <c r="R13" t="n">
         <v>6869470</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124556002</v>
+        <v>124555207</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1997,7 +2002,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2007,17 +2012,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491116</v>
+        <v>491027</v>
       </c>
       <c r="R14" t="n">
-        <v>6869470</v>
+        <v>6869192</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2061,19 +2066,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555260</v>
+        <v>124555800</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2109,17 +2114,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490993</v>
+        <v>491078</v>
       </c>
       <c r="R15" t="n">
-        <v>6869192</v>
+        <v>6869479</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2163,19 +2168,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555235</v>
+        <v>124555994</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2220,17 +2225,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491014</v>
+        <v>491147</v>
       </c>
       <c r="R16" t="n">
-        <v>6869213</v>
+        <v>6869404</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,22 +2279,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555442</v>
+        <v>124555341</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,37 +2307,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490962</v>
+        <v>490971</v>
       </c>
       <c r="R17" t="n">
-        <v>6869305</v>
+        <v>6869235</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2362,11 +2367,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,22 +2381,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555517</v>
+        <v>124555280</v>
       </c>
       <c r="B18" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,21 +2409,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491020</v>
+        <v>491004</v>
       </c>
       <c r="R18" t="n">
-        <v>6869351</v>
+        <v>6869214</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555994</v>
+        <v>124555269</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491147</v>
+        <v>491017</v>
       </c>
       <c r="R19" t="n">
-        <v>6869404</v>
+        <v>6869226</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2594,12 +2594,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -2393,10 +2393,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555280</v>
+        <v>124555269</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,38 +2405,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491004</v>
+        <v>491017</v>
       </c>
       <c r="R18" t="n">
-        <v>6869214</v>
+        <v>6869226</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2495,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555269</v>
+        <v>124555280</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,47 +2516,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491017</v>
+        <v>491004</v>
       </c>
       <c r="R19" t="n">
-        <v>6869226</v>
+        <v>6869214</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 31584-2024 artfynd.xlsx
+++ b/artfynd/A 31584-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124555442</v>
+        <v>124555207</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490962</v>
+        <v>491027</v>
       </c>
       <c r="R2" t="n">
-        <v>6869305</v>
+        <v>6869192</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -893,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124555216</v>
+        <v>124556002</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -942,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491016</v>
+        <v>491116</v>
       </c>
       <c r="R4" t="n">
-        <v>6869188</v>
+        <v>6869470</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124555260</v>
+        <v>124555994</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,38 +1020,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490993</v>
+        <v>491147</v>
       </c>
       <c r="R5" t="n">
-        <v>6869192</v>
+        <v>6869404</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124555517</v>
+        <v>124555341</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491020</v>
+        <v>490971</v>
       </c>
       <c r="R6" t="n">
-        <v>6869351</v>
+        <v>6869235</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1208,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124555235</v>
+        <v>124555800</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,47 +1233,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491014</v>
+        <v>491078</v>
       </c>
       <c r="R7" t="n">
-        <v>6869213</v>
+        <v>6869479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124555253</v>
+        <v>124555773</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,50 +1335,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491020</v>
+        <v>491115</v>
       </c>
       <c r="R8" t="n">
-        <v>6869220</v>
+        <v>6869473</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,22 +1413,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124555289</v>
+        <v>124555280</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,50 +1437,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491008</v>
+        <v>491004</v>
       </c>
       <c r="R9" t="n">
         <v>6869214</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1515,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124555221</v>
+        <v>124555442</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,50 +1539,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491024</v>
+        <v>490962</v>
       </c>
       <c r="R10" t="n">
-        <v>6869198</v>
+        <v>6869305</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,6 +1603,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124555330</v>
+        <v>124555216</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,41 +1646,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490997</v>
+        <v>491016</v>
       </c>
       <c r="R11" t="n">
-        <v>6869240</v>
+        <v>6869188</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,19 +1733,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124555773</v>
+        <v>124555330</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1794,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491115</v>
+        <v>490997</v>
       </c>
       <c r="R12" t="n">
-        <v>6869473</v>
+        <v>6869240</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124556002</v>
+        <v>124555235</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1891,7 +1882,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1905,13 +1896,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491116</v>
+        <v>491014</v>
       </c>
       <c r="R13" t="n">
-        <v>6869470</v>
+        <v>6869213</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124555207</v>
+        <v>124555260</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,44 +1970,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491027</v>
+        <v>490993</v>
       </c>
       <c r="R14" t="n">
         <v>6869192</v>
@@ -2078,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124555800</v>
+        <v>124555269</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,41 +2072,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491078</v>
+        <v>491017</v>
       </c>
       <c r="R15" t="n">
-        <v>6869479</v>
+        <v>6869226</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2180,10 +2171,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124555994</v>
+        <v>124555517</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,50 +2183,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
+          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491147</v>
+        <v>491020</v>
       </c>
       <c r="R16" t="n">
-        <v>6869404</v>
+        <v>6869351</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2279,22 +2261,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124555341</v>
+        <v>124555253</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,41 +2285,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490971</v>
+        <v>491020</v>
       </c>
       <c r="R17" t="n">
-        <v>6869235</v>
+        <v>6869220</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,7 +2384,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124555269</v>
+        <v>124555221</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2428,7 +2419,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2438,17 +2429,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491017</v>
+        <v>491024</v>
       </c>
       <c r="R18" t="n">
-        <v>6869226</v>
+        <v>6869198</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,22 +2483,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124555280</v>
+        <v>124555289</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,41 +2507,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandtjärnbäcken, Sandtjärnbäcken, Hls</t>
+          <t>Jo-Kallsåsen, Jo-Kallsåsen, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491004</v>
+        <v>491008</v>
       </c>
       <c r="R19" t="n">
         <v>6869214</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2594,12 +2594,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
